--- a/订单数据.xlsx
+++ b/订单数据.xlsx
@@ -569,6 +569,9 @@
       </c>
     </row>
     <row r="6">
+      <c r="C6" t="str">
+        <v>1</v>
+      </c>
       <c r="E6" t="str">
         <v>拓竹PLA Matte哑光 3D打印耗材 高韧性易剥离高速易打印 RFID智能参数识别</v>
       </c>
@@ -2092,198 +2095,6 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="190">
-    <mergeCell ref="A2"/>
-    <mergeCell ref="B2"/>
-    <mergeCell ref="C2"/>
-    <mergeCell ref="D2"/>
-    <mergeCell ref="J2"/>
-    <mergeCell ref="K2"/>
-    <mergeCell ref="A3"/>
-    <mergeCell ref="B3"/>
-    <mergeCell ref="C3"/>
-    <mergeCell ref="D3"/>
-    <mergeCell ref="J3"/>
-    <mergeCell ref="K3"/>
-    <mergeCell ref="A4:A9"/>
-    <mergeCell ref="B4:B9"/>
-    <mergeCell ref="C4:C9"/>
-    <mergeCell ref="D4:D9"/>
-    <mergeCell ref="J4:J9"/>
-    <mergeCell ref="K4:K9"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="B10:B12"/>
-    <mergeCell ref="C10:C12"/>
-    <mergeCell ref="D10:D12"/>
-    <mergeCell ref="J10:J12"/>
-    <mergeCell ref="K10:K12"/>
-    <mergeCell ref="A13"/>
-    <mergeCell ref="B13"/>
-    <mergeCell ref="C13"/>
-    <mergeCell ref="D13"/>
-    <mergeCell ref="J13"/>
-    <mergeCell ref="K13"/>
-    <mergeCell ref="A14"/>
-    <mergeCell ref="B14"/>
-    <mergeCell ref="C14"/>
-    <mergeCell ref="D14"/>
-    <mergeCell ref="J14"/>
-    <mergeCell ref="K14"/>
-    <mergeCell ref="A15"/>
-    <mergeCell ref="B15"/>
-    <mergeCell ref="C15"/>
-    <mergeCell ref="D15"/>
-    <mergeCell ref="J15"/>
-    <mergeCell ref="K15"/>
-    <mergeCell ref="A16"/>
-    <mergeCell ref="B16"/>
-    <mergeCell ref="C16"/>
-    <mergeCell ref="D16"/>
-    <mergeCell ref="J16"/>
-    <mergeCell ref="K16"/>
-    <mergeCell ref="A17"/>
-    <mergeCell ref="B17"/>
-    <mergeCell ref="C17"/>
-    <mergeCell ref="D17"/>
-    <mergeCell ref="J17"/>
-    <mergeCell ref="K17"/>
-    <mergeCell ref="A18"/>
-    <mergeCell ref="B18"/>
-    <mergeCell ref="C18"/>
-    <mergeCell ref="D18"/>
-    <mergeCell ref="J18"/>
-    <mergeCell ref="K18"/>
-    <mergeCell ref="A19"/>
-    <mergeCell ref="B19"/>
-    <mergeCell ref="C19"/>
-    <mergeCell ref="D19"/>
-    <mergeCell ref="J19"/>
-    <mergeCell ref="K19"/>
-    <mergeCell ref="A20"/>
-    <mergeCell ref="B20"/>
-    <mergeCell ref="C20"/>
-    <mergeCell ref="D20"/>
-    <mergeCell ref="J20"/>
-    <mergeCell ref="K20"/>
-    <mergeCell ref="A21"/>
-    <mergeCell ref="B21"/>
-    <mergeCell ref="C21"/>
-    <mergeCell ref="D21"/>
-    <mergeCell ref="J21"/>
-    <mergeCell ref="K21"/>
-    <mergeCell ref="A22"/>
-    <mergeCell ref="B22"/>
-    <mergeCell ref="C22"/>
-    <mergeCell ref="D22"/>
-    <mergeCell ref="J22"/>
-    <mergeCell ref="K22"/>
-    <mergeCell ref="A23"/>
-    <mergeCell ref="B23"/>
-    <mergeCell ref="C23"/>
-    <mergeCell ref="D23"/>
-    <mergeCell ref="J23"/>
-    <mergeCell ref="K23"/>
-    <mergeCell ref="A24:A27"/>
-    <mergeCell ref="B24:B27"/>
-    <mergeCell ref="C24:C27"/>
-    <mergeCell ref="D24:D27"/>
-    <mergeCell ref="J24:J27"/>
-    <mergeCell ref="K24:K27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="J28:J29"/>
-    <mergeCell ref="K28:K29"/>
-    <mergeCell ref="A30"/>
-    <mergeCell ref="B30"/>
-    <mergeCell ref="C30"/>
-    <mergeCell ref="D30"/>
-    <mergeCell ref="J30"/>
-    <mergeCell ref="K30"/>
-    <mergeCell ref="A31"/>
-    <mergeCell ref="B31"/>
-    <mergeCell ref="C31"/>
-    <mergeCell ref="D31"/>
-    <mergeCell ref="J31"/>
-    <mergeCell ref="K31"/>
-    <mergeCell ref="A32:A37"/>
-    <mergeCell ref="B32:B37"/>
-    <mergeCell ref="C32:C37"/>
-    <mergeCell ref="D32:D37"/>
-    <mergeCell ref="J32:J37"/>
-    <mergeCell ref="K32:K37"/>
-    <mergeCell ref="A38:A42"/>
-    <mergeCell ref="B38:B42"/>
-    <mergeCell ref="C38:C42"/>
-    <mergeCell ref="D38:D42"/>
-    <mergeCell ref="J38:J42"/>
-    <mergeCell ref="K38:K42"/>
-    <mergeCell ref="A43"/>
-    <mergeCell ref="B43"/>
-    <mergeCell ref="C43"/>
-    <mergeCell ref="D43"/>
-    <mergeCell ref="J43"/>
-    <mergeCell ref="K43"/>
-    <mergeCell ref="A44"/>
-    <mergeCell ref="B44"/>
-    <mergeCell ref="C44"/>
-    <mergeCell ref="D44"/>
-    <mergeCell ref="J44"/>
-    <mergeCell ref="K44"/>
-    <mergeCell ref="A45:A48"/>
-    <mergeCell ref="B45:B48"/>
-    <mergeCell ref="C45:C48"/>
-    <mergeCell ref="D45:D48"/>
-    <mergeCell ref="J45:J48"/>
-    <mergeCell ref="K45:K48"/>
-    <mergeCell ref="A49"/>
-    <mergeCell ref="B49"/>
-    <mergeCell ref="C49"/>
-    <mergeCell ref="D49"/>
-    <mergeCell ref="J49"/>
-    <mergeCell ref="K49"/>
-    <mergeCell ref="A50"/>
-    <mergeCell ref="B50"/>
-    <mergeCell ref="C50"/>
-    <mergeCell ref="D50"/>
-    <mergeCell ref="J50"/>
-    <mergeCell ref="K50"/>
-    <mergeCell ref="A51"/>
-    <mergeCell ref="B51"/>
-    <mergeCell ref="C51"/>
-    <mergeCell ref="D51"/>
-    <mergeCell ref="J51"/>
-    <mergeCell ref="K51"/>
-    <mergeCell ref="A52"/>
-    <mergeCell ref="B52"/>
-    <mergeCell ref="C52"/>
-    <mergeCell ref="D52"/>
-    <mergeCell ref="J52"/>
-    <mergeCell ref="K52"/>
-    <mergeCell ref="A53"/>
-    <mergeCell ref="B53"/>
-    <mergeCell ref="C53"/>
-    <mergeCell ref="D53"/>
-    <mergeCell ref="J53"/>
-    <mergeCell ref="K53"/>
-    <mergeCell ref="A54"/>
-    <mergeCell ref="B54"/>
-    <mergeCell ref="C54"/>
-    <mergeCell ref="D54"/>
-    <mergeCell ref="J54"/>
-    <mergeCell ref="K54"/>
-    <mergeCell ref="E45:E46"/>
-    <mergeCell ref="F45:F46"/>
-    <mergeCell ref="I45:I46"/>
-    <mergeCell ref="H45:H46"/>
-    <mergeCell ref="G45:G46"/>
-    <mergeCell ref="E47:E48"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="I47:I48"/>
-    <mergeCell ref="H47:H48"/>
-    <mergeCell ref="G47:G48"/>
-  </mergeCells>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:M54"/>
   </ignoredErrors>
